--- a/outputs/reports/catboost_v1/feature_importance_top10.xlsx
+++ b/outputs/reports/catboost_v1/feature_importance_top10.xlsx
@@ -479,10 +479,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0720834366819162</v>
+        <v>0.06512370292287779</v>
       </c>
       <c r="F2" t="n">
-        <v>7.208343668191625</v>
+        <v>6.512370292287774</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=7.21%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.51%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -515,10 +515,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.06054513955043873</v>
+        <v>0.06218461134590617</v>
       </c>
       <c r="F3" t="n">
-        <v>6.054513955043876</v>
+        <v>6.218461134590611</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.05%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.22%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.05896145497730271</v>
+        <v>0.0586404025870892</v>
       </c>
       <c r="F4" t="n">
-        <v>5.896145497730275</v>
+        <v>5.864040258708916</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.90%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.86%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LAF_CPRN_AID_BIZCT_RT</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>지자체대비보조사업금액비율</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05096941996978932</v>
+        <v>0.04820782632383652</v>
       </c>
       <c r="F5" t="n">
-        <v>5.096941996978935</v>
+        <v>4.820782632383648</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=5.10%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.82%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.04933380106314258</v>
+        <v>0.04747477439020054</v>
       </c>
       <c r="F6" t="n">
-        <v>4.933380106314261</v>
+        <v>4.74747743902005</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.93%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.75%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04914549675775322</v>
+        <v>0.04480735044966697</v>
       </c>
       <c r="F7" t="n">
-        <v>4.914549675775325</v>
+        <v>4.480735044966694</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.91%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -686,19 +686,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04751753225903853</v>
+        <v>0.04033593740657232</v>
       </c>
       <c r="F8" t="n">
-        <v>4.751753225903856</v>
+        <v>4.033593740657229</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=4.75%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.03%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -722,19 +722,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>인건비계획비율</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04720868290349021</v>
+        <v>0.03634252123369216</v>
       </c>
       <c r="F9" t="n">
-        <v>4.720868290349023</v>
+        <v>3.634252123369213</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.72%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=3.63%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.04484785765179874</v>
+        <v>0.03377831181233264</v>
       </c>
       <c r="F10" t="n">
-        <v>4.484785765179876</v>
+        <v>3.377831181233262</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=3.38%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.03747459357124595</v>
+        <v>0.03369229173308515</v>
       </c>
       <c r="F11" t="n">
-        <v>3.747459357124598</v>
+        <v>3.369229173308512</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.75%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.37%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>

--- a/outputs/reports/catboost_v1/feature_importance_top10.xlsx
+++ b/outputs/reports/catboost_v1/feature_importance_top10.xlsx
@@ -470,19 +470,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.06512370292287779</v>
+        <v>0.06671461789117154</v>
       </c>
       <c r="F2" t="n">
-        <v>6.512370292287774</v>
+        <v>6.671461789117155</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.51%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.67%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -506,19 +506,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.06218461134590617</v>
+        <v>0.06495441989195058</v>
       </c>
       <c r="F3" t="n">
-        <v>6.218461134590611</v>
+        <v>6.495441989195059</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.22%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.50%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -542,19 +542,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.0586404025870892</v>
+        <v>0.05547755973096497</v>
       </c>
       <c r="F4" t="n">
-        <v>5.864040258708916</v>
+        <v>5.547755973096498</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.86%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=5.55%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.04820782632383652</v>
+        <v>0.05417814811546744</v>
       </c>
       <c r="F5" t="n">
-        <v>4.820782632383648</v>
+        <v>5.417814811546745</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.82%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=5.42%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.04747477439020054</v>
+        <v>0.05058522443296955</v>
       </c>
       <c r="F6" t="n">
-        <v>4.74747743902005</v>
+        <v>5.058522443296956</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.75%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -650,19 +650,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04480735044966697</v>
+        <v>0.04458071949171321</v>
       </c>
       <c r="F7" t="n">
-        <v>4.480735044966694</v>
+        <v>4.458071949171321</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.46%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -686,19 +686,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04033593740657232</v>
+        <v>0.04060187085898578</v>
       </c>
       <c r="F8" t="n">
-        <v>4.033593740657229</v>
+        <v>4.060187085898579</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.03%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -722,19 +722,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LBST_PLAN_RT</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>인건비계획비율</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03634252123369216</v>
+        <v>0.03611816776722611</v>
       </c>
       <c r="F9" t="n">
-        <v>3.634252123369213</v>
+        <v>3.611816776722611</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=3.63%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.61%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BIZ_MDCN</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>사업개월수</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03377831181233264</v>
+        <v>0.03477271178468273</v>
       </c>
       <c r="F10" t="n">
-        <v>3.377831181233262</v>
+        <v>3.477271178468274</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=3.38%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>인건비계획비율</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.03369229173308515</v>
+        <v>0.0344039068366</v>
       </c>
       <c r="F11" t="n">
-        <v>3.369229173308512</v>
+        <v>3.44039068366</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.37%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=3.44%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>

--- a/outputs/reports/catboost_v1/feature_importance_top10.xlsx
+++ b/outputs/reports/catboost_v1/feature_importance_top10.xlsx
@@ -470,19 +470,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.06671461789117154</v>
+        <v>0.06762103693331124</v>
       </c>
       <c r="F2" t="n">
-        <v>6.671461789117155</v>
+        <v>6.762103693331121</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.67%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.76%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -506,19 +506,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.06495441989195058</v>
+        <v>0.06558865971786301</v>
       </c>
       <c r="F3" t="n">
-        <v>6.495441989195059</v>
+        <v>6.558865971786298</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.50%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.56%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -542,19 +542,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.05547755973096497</v>
+        <v>0.05638176459826573</v>
       </c>
       <c r="F4" t="n">
-        <v>5.547755973096498</v>
+        <v>5.63817645982657</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=5.55%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.64%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05417814811546744</v>
+        <v>0.04176772834277437</v>
       </c>
       <c r="F5" t="n">
-        <v>5.417814811546745</v>
+        <v>4.176772834277435</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=5.42%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.18%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.05058522443296955</v>
+        <v>0.04140493817864251</v>
       </c>
       <c r="F6" t="n">
-        <v>5.058522443296956</v>
+        <v>4.140493817864249</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.14%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -650,19 +650,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04458071949171321</v>
+        <v>0.03586576551426982</v>
       </c>
       <c r="F7" t="n">
-        <v>4.458071949171321</v>
+        <v>3.58657655142698</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.46%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=3.59%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -686,19 +686,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04060187085898578</v>
+        <v>0.03486040528587571</v>
       </c>
       <c r="F8" t="n">
-        <v>4.060187085898579</v>
+        <v>3.486040528587569</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=3.49%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -722,19 +722,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03611816776722611</v>
+        <v>0.03306797514035693</v>
       </c>
       <c r="F9" t="n">
-        <v>3.611816776722611</v>
+        <v>3.306797514035692</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.61%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.31%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>FLD_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>분야코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03477271178468273</v>
+        <v>0.03270175100360688</v>
       </c>
       <c r="F10" t="n">
-        <v>3.477271178468274</v>
+        <v>3.270175100360686</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 분야코드(FLD_CD). 기여도(정규화 비중)=3.27%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LBST_PLAN_RT</t>
+          <t>LAF_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>인건비계획비율</t>
+          <t>지자체수행보조사업수</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0344039068366</v>
+        <v>0.02953478423868656</v>
       </c>
       <c r="F11" t="n">
-        <v>3.44039068366</v>
+        <v>2.953478423868654</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=3.44%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지자체수행보조사업수(LAF_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=2.95%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
